--- a/output/roomself_excel/10132.xlsx
+++ b/output/roomself_excel/10132.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>54736</v>
+        <v>132816</v>
       </c>
       <c r="D2" t="n">
-        <v>1948</v>
+        <v>2992</v>
       </c>
       <c r="E2" t="n">
-        <v>337</v>
+        <v>296</v>
       </c>
       <c r="F2" t="n">
-        <v>189</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>189285</v>
+        <v>234252</v>
       </c>
       <c r="D3" t="n">
-        <v>3628</v>
+        <v>3872</v>
       </c>
       <c r="E3" t="n">
-        <v>576</v>
+        <v>482</v>
       </c>
       <c r="F3" t="n">
-        <v>575</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>484876</v>
+        <v>125341</v>
       </c>
       <c r="D6" t="n">
-        <v>8488</v>
+        <v>3052</v>
       </c>
       <c r="E6" t="n">
-        <v>1153</v>
+        <v>498</v>
       </c>
       <c r="F6" t="n">
-        <v>939</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>307868</v>
+        <v>21079</v>
       </c>
       <c r="D7" t="n">
-        <v>5292</v>
+        <v>1216</v>
       </c>
       <c r="E7" t="n">
-        <v>594</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>576</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21079</v>
+        <v>37696</v>
       </c>
       <c r="D8" t="n">
-        <v>1216</v>
+        <v>1712</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>331</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>44325</v>
+        <v>96255</v>
       </c>
       <c r="D9" t="n">
-        <v>1688</v>
+        <v>2496</v>
       </c>
       <c r="E9" t="n">
-        <v>197</v>
+        <v>372</v>
       </c>
       <c r="F9" t="n">
-        <v>27</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>37696</v>
+        <v>117808</v>
       </c>
       <c r="D10" t="n">
-        <v>1712</v>
+        <v>4672</v>
       </c>
       <c r="E10" t="n">
-        <v>331</v>
+        <v>465</v>
       </c>
       <c r="F10" t="n">
-        <v>135</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>125341</v>
+        <v>13542</v>
       </c>
       <c r="D11" t="n">
-        <v>3052</v>
+        <v>932</v>
       </c>
       <c r="E11" t="n">
-        <v>498</v>
+        <v>122</v>
       </c>
       <c r="F11" t="n">
-        <v>466</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>96255</v>
+        <v>54736</v>
       </c>
       <c r="D12" t="n">
-        <v>2496</v>
+        <v>1948</v>
       </c>
       <c r="E12" t="n">
-        <v>372</v>
+        <v>337</v>
       </c>
       <c r="F12" t="n">
-        <v>304</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13">
@@ -708,19 +708,63 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>13542</v>
+        <v>189285</v>
       </c>
       <c r="D13" t="n">
-        <v>932</v>
+        <v>3628</v>
       </c>
       <c r="E13" t="n">
-        <v>122</v>
+        <v>576</v>
       </c>
       <c r="F13" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>307868</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5292</v>
+      </c>
+      <c r="E14" t="n">
+        <v>581</v>
+      </c>
+      <c r="F14" t="n">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>44325</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1688</v>
+      </c>
+      <c r="E15" t="n">
+        <v>197</v>
+      </c>
+      <c r="F15" t="n">
         <v>27</v>
       </c>
     </row>

--- a/output/roomself_excel/10132.xlsx
+++ b/output/roomself_excel/10132.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,10 +495,26 @@
       <c r="D2" t="n">
         <v>2992</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>444</v>
+      </c>
+      <c r="G2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>296</v>
       </c>
-      <c r="F2" t="n">
+      <c r="J2" t="n">
         <v>27</v>
       </c>
     </row>
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>3872</v>
       </c>
-      <c r="E3" t="n">
-        <v>482</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>27</v>
+        <v>470</v>
+      </c>
+      <c r="G3" t="n">
+        <v>27</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>486</v>
+      </c>
+      <c r="J3" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +571,27 @@
       <c r="D4" t="n">
         <v>3080</v>
       </c>
-      <c r="E4" t="n">
-        <v>453</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>372</v>
+        <v>345</v>
+      </c>
+      <c r="G4" t="n">
+        <v>28</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>425</v>
+      </c>
+      <c r="J4" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -541,11 +609,27 @@
       <c r="D5" t="n">
         <v>3144</v>
       </c>
-      <c r="E5" t="n">
-        <v>445</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>395</v>
+        <v>418</v>
+      </c>
+      <c r="G5" t="n">
+        <v>27</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>368</v>
+      </c>
+      <c r="J5" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -563,11 +647,27 @@
       <c r="D6" t="n">
         <v>3052</v>
       </c>
-      <c r="E6" t="n">
-        <v>498</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>319</v>
+        <v>292</v>
+      </c>
+      <c r="G6" t="n">
+        <v>27</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>459</v>
+      </c>
+      <c r="J6" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -585,12 +685,12 @@
       <c r="D7" t="n">
         <v>1216</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +707,27 @@
       <c r="D8" t="n">
         <v>1712</v>
       </c>
-      <c r="E8" t="n">
-        <v>331</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>135</v>
+        <v>124</v>
+      </c>
+      <c r="G8" t="n">
+        <v>27</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>157</v>
+      </c>
+      <c r="J8" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -629,11 +745,27 @@
       <c r="D9" t="n">
         <v>2496</v>
       </c>
-      <c r="E9" t="n">
-        <v>372</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>304</v>
+        <v>279</v>
+      </c>
+      <c r="G9" t="n">
+        <v>27</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>345</v>
+      </c>
+      <c r="J9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -651,11 +783,27 @@
       <c r="D10" t="n">
         <v>4672</v>
       </c>
-      <c r="E10" t="n">
-        <v>465</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>122</v>
+        <v>110</v>
+      </c>
+      <c r="G10" t="n">
+        <v>27</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>88</v>
+      </c>
+      <c r="J10" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -673,12 +821,20 @@
       <c r="D11" t="n">
         <v>932</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>122</v>
       </c>
-      <c r="F11" t="n">
-        <v>27</v>
-      </c>
+      <c r="G11" t="n">
+        <v>27</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,11 +851,27 @@
       <c r="D12" t="n">
         <v>1948</v>
       </c>
-      <c r="E12" t="n">
-        <v>337</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>189</v>
+        <v>311</v>
+      </c>
+      <c r="G12" t="n">
+        <v>13</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>352</v>
+      </c>
+      <c r="J12" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -717,11 +889,27 @@
       <c r="D13" t="n">
         <v>3628</v>
       </c>
-      <c r="E13" t="n">
-        <v>576</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>386</v>
+        <v>358</v>
+      </c>
+      <c r="G13" t="n">
+        <v>27</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>228</v>
+      </c>
+      <c r="J13" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="14">
@@ -739,11 +927,27 @@
       <c r="D14" t="n">
         <v>5292</v>
       </c>
-      <c r="E14" t="n">
-        <v>581</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>576</v>
+        <v>556</v>
+      </c>
+      <c r="G14" t="n">
+        <v>27</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>549</v>
+      </c>
+      <c r="J14" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -761,12 +965,20 @@
       <c r="D15" t="n">
         <v>1688</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>197</v>
       </c>
-      <c r="F15" t="n">
-        <v>27</v>
-      </c>
+      <c r="G15" t="n">
+        <v>27</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
